--- a/data/ordbok_konfidensialitet.xlsx
+++ b/data/ordbok_konfidensialitet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ssbno-my.sharepoint.com/personal/ibi_ssb_no/Documents/Skrivebord/Ordbok Ingrid/Utkast ordbok/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="254" documentId="8_{19116777-D8DD-4556-9A16-9CDC6F0D346F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52D27DDF-57AD-462B-B0F5-22C3748E6BEC}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="8_{19116777-D8DD-4556-9A16-9CDC6F0D346F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0912CB94-CDA5-4258-8D90-3B8005A0FE41}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ordbok" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
   <si>
     <t>Ordbok for konfidensialitetsbegreper</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Anonymised data</t>
   </si>
   <si>
-    <t>Attribuering</t>
-  </si>
-  <si>
     <t>Attribution</t>
   </si>
   <si>
@@ -83,12 +80,6 @@
     <t>Differencing</t>
   </si>
   <si>
-    <t>Dominansregel</t>
-  </si>
-  <si>
-    <t>Dominance rule</t>
-  </si>
-  <si>
     <t>Global omkoding</t>
   </si>
   <si>
@@ -98,30 +89,15 @@
     <t>Intruder</t>
   </si>
   <si>
-    <t>Lokal omkoding</t>
-  </si>
-  <si>
-    <t>Local recoding</t>
-  </si>
-  <si>
     <t>Terskelregel</t>
   </si>
   <si>
     <t>Threshold rule</t>
   </si>
   <si>
-    <t>Toppkoding og bunnkoding</t>
-  </si>
-  <si>
-    <t>Top and bottom coding</t>
-  </si>
-  <si>
     <t>Suppression</t>
   </si>
   <si>
-    <t>Sammenkobling eller frakobling mellom et bestemt kjennetegn og en bestemt populasjonsenhet.</t>
-  </si>
-  <si>
     <t>Identifikator</t>
   </si>
   <si>
@@ -131,9 +107,6 @@
     <t>p%-regel</t>
   </si>
   <si>
-    <t>(p,q)-regel</t>
-  </si>
-  <si>
     <t>Støylegging</t>
   </si>
   <si>
@@ -146,9 +119,6 @@
     <t>p%-rule</t>
   </si>
   <si>
-    <t>(p,q)-rule</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pseudonomysation </t>
   </si>
   <si>
@@ -176,12 +146,6 @@
     <t>Hundepool et al, s. 212</t>
   </si>
   <si>
-    <t>Dette vil gi noen avvik fra de opprinnelige tallene, men metoden fungerer slik at avvikene er små og ikke betyr mye for tolkningen av resultatene.</t>
-  </si>
-  <si>
-    <t>En metode der det settes en øvre og/eller nedre grense (hhv. toppkode og bunnkode) for kvantitative variabler. Verdier over/under grensen blir enten ikke publisert, eller så erstattes de med grenseverdien.</t>
-  </si>
-  <si>
     <t>Hundepool et al, s. 226; Heldal (Ordliste)</t>
   </si>
   <si>
@@ -206,36 +170,12 @@
     <t>Hundepool et al, s. 216; Heldal (Ordliste)</t>
   </si>
   <si>
-    <t xml:space="preserve">En metode for å hindre avsløring der ulike inndelinger av en variabel brukes for ulike grupper i dataene. I tilfeller der fordelingen er skjev kan små kategorier kombineres, slik at variabelen blir grovere. </t>
-  </si>
-  <si>
-    <t>Hundepool et al, s. 218; Heldal (Ordliste)</t>
-  </si>
-  <si>
     <t>Hundepool et al, s. 220 &amp; 223; Heldal (Ordliste)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hundepool et al, s. 220 </t>
-  </si>
-  <si>
-    <t>Verdiene for p og q fastsettes av statistikkmyndigheten og uttrykker hvilket nivå av informasjonsgevinst som aksepteres.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regelen er et spesialtilfelle av (p, q)-regelen der q er satt til 100. </t>
-  </si>
-  <si>
     <t>Hundepool et al, s. 220; Heldal (Ordliste)</t>
   </si>
   <si>
-    <t xml:space="preserve">Regel som sier at en celle må undertrykkes hvis informasjonsgevinsten publisering vil gi gjør det mulig å estimere en enhets bidrag til cellen i for stor grad. Informasjonsgevinsten ved publisering måles ved forholdet mellom feilmarginen etter (p) og før (q) publisering. </t>
-  </si>
-  <si>
-    <t>(Tilfeldig) avrunding</t>
-  </si>
-  <si>
-    <t>(Random) rounding</t>
-  </si>
-  <si>
     <t>Hundepool et al, s. 219; Heldal (Ordliste)</t>
   </si>
   <si>
@@ -287,35 +227,71 @@
     <t xml:space="preserve">Regel som sier at en celle i en frekvenstabell ikke kan publiseres dersom antallet enheter i cellen er lavere enn en fastsatt terskel, og at en celle i en volumtabell ikke kan publiseres dersom antallet enheter som bidrar til celletotalen er under en fastsatt terskel. </t>
   </si>
   <si>
-    <t>En metode for å hindre avsløring der verdiene i et datasett eller en tabell endres for å bevisst introdusere usikkerhet. De statistiske egenskapene til dataen bevares best mulig.</t>
-  </si>
-  <si>
     <t>En metode for å hindre avsløring der enkelte celleverdier ikke offentliggjøres, men erstattes med et symbol for å vise at de har blitt undertrykket. Undertrykking kalles ofte for "prikking".</t>
   </si>
   <si>
     <t xml:space="preserve">En metode for å hindre avsløring der rader eller kolonner i tabeller slås sammen ved å lage større intervaller eller grupperinger, eller der flere variabelkategorier i mikrodata slås sammen.  </t>
   </si>
   <si>
-    <t>Regel som sier at en celle må undertrykkes dersom de n største enhetene bidrar med mer enn k% av celletotalen.</t>
-  </si>
-  <si>
     <t>Regelen kalles ofte for (n, k)-regelen.  Verdiene for n og k fastsettes av statistikkmyndigheten.</t>
   </si>
   <si>
-    <t>Variabel som alene eller i kombinasjon er strukturelt unik og dermed kan brukes til å identifisere statistiske enheter i et datasett.</t>
-  </si>
-  <si>
-    <t>En metode der celleverdier avrundes tilfeldig opp eller ned til en av de nærmeste multiplene av et gitt basetall.</t>
-  </si>
-  <si>
     <t>Data der det ikke er mulig, ved hjelp av de opplysningene som inngår i datasettet og alle rimelige tekniske hjelpemidler, å knytte opplysningene til en enkeltperson eller en annen statistisk enhet.</t>
+  </si>
+  <si>
+    <t>Sammenkobling mellom et kjennetegn og en statistisk enhet, der informasjon om hvorvidt enheten har eller ikke har kjennetegnet kan utledes.</t>
+  </si>
+  <si>
+    <t>Attribusjon</t>
+  </si>
+  <si>
+    <t>Avrunding</t>
+  </si>
+  <si>
+    <t>Rounding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En metode for å hindre avsløring der små celleverdier avrundes tilfeldig opp eller ned til en av de nærmeste multiplene av et gitt basetall. Summer vil dermed omfatte tall som er avrundet, men metoden forsøker å beholde summene på aggregert nivå så like de ikke-avrundede tallene som mulig. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toppkoding </t>
+  </si>
+  <si>
+    <t>Top coding</t>
+  </si>
+  <si>
+    <t>Bunnkoding</t>
+  </si>
+  <si>
+    <t>Bottom coding</t>
+  </si>
+  <si>
+    <t>En metode for å hindre avsløring der det settes en øvre grense for kvantitative variabler. Verdier over grensen blir enten ikke publisert, eller så erstattes de med grenseverdien.</t>
+  </si>
+  <si>
+    <t>En metode for å hindre avsløring der det settes en nedre grense for kvantitative variabler. Verdier under grensen blir enten ikke publisert, eller så erstattes de med grenseverdien.</t>
+  </si>
+  <si>
+    <t>Variabel som alene eller i kombinasjon med andre er strukturelt unik og dermed kan brukes til å identifisere statistiske enheter i et datasett.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regel som sier at en celle må undertrykkes dersom de n største bidragsyterne står for mer enn k% av celletotalen. </t>
+  </si>
+  <si>
+    <t>(n,k)-regel</t>
+  </si>
+  <si>
+    <t>(n,k)-rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En metode for å hindre avsløring der verdiene i et datasett eller en tabell endres for å introdusere usikkerhet. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,6 +347,14 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -450,13 +434,13 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperkobling" xfId="1" builtinId="8"/>
@@ -760,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
@@ -771,14 +755,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -794,7 +778,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -802,473 +786,457 @@
     </row>
     <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="A8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="5"/>
+      <c r="E11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="5"/>
+      <c r="C14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>61</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="A17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="A19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="4"/>
+      <c r="D19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>67</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="4"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
     </row>
     <row r="34" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
     </row>
     <row r="35" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
     </row>
     <row r="36" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2"/>
@@ -1279,316 +1247,316 @@
       <c r="F36" s="2"/>
     </row>
     <row r="37" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
     </row>
     <row r="39" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
     </row>
     <row r="41" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
     </row>
     <row r="43" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
     </row>
     <row r="47" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
     </row>
     <row r="49" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
     </row>
     <row r="51" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
     </row>
     <row r="53" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
     </row>
     <row r="54" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
     </row>
     <row r="55" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
     </row>
     <row r="57" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
     </row>
     <row r="58" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
     </row>
     <row r="59" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
     </row>
     <row r="60" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
     </row>
     <row r="61" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
     </row>
     <row r="62" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
     </row>
     <row r="63" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
     </row>
     <row r="64" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
     </row>
     <row r="66" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
     </row>
     <row r="68" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
     </row>
     <row r="69" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
     </row>
     <row r="70" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
     </row>
     <row r="71" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
     </row>
     <row r="72" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
     </row>
     <row r="73" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
     </row>
     <row r="74" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
     </row>
     <row r="75" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
     </row>
     <row r="76" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
@@ -1599,84 +1567,84 @@
       <c r="F76" s="3"/>
     </row>
     <row r="77" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
     </row>
     <row r="78" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
     </row>
     <row r="80" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
     </row>
     <row r="81" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
     </row>
     <row r="82" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
     </row>
     <row r="83" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
     </row>
     <row r="84" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
     </row>
     <row r="85" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
     </row>
     <row r="86" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
     </row>
     <row r="87" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
@@ -1687,28 +1655,28 @@
       <c r="F87" s="3"/>
     </row>
     <row r="88" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
     </row>
     <row r="89" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
     </row>
     <row r="90" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
     </row>
     <row r="91" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2"/>
@@ -1719,92 +1687,92 @@
       <c r="F91" s="2"/>
     </row>
     <row r="92" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
     </row>
     <row r="94" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
     </row>
     <row r="95" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
     </row>
     <row r="96" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
     </row>
     <row r="97" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
     </row>
     <row r="98" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
     </row>
     <row r="99" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
     </row>
     <row r="100" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
     </row>
     <row r="101" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
     </row>
     <row r="102" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
     </row>
     <row r="103" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
@@ -1823,12 +1791,12 @@
       <c r="F104" s="3"/>
     </row>
     <row r="105" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
     </row>
     <row r="106" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2"/>
@@ -1839,44 +1807,44 @@
       <c r="F106" s="2"/>
     </row>
     <row r="107" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
     </row>
     <row r="108" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
     </row>
     <row r="109" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
     </row>
     <row r="110" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
     </row>
     <row r="111" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
     </row>
     <row r="112" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
@@ -1895,28 +1863,28 @@
       <c r="F113" s="3"/>
     </row>
     <row r="114" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
     </row>
     <row r="115" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
     </row>
     <row r="116" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
     </row>
     <row r="117" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2"/>
@@ -1926,21 +1894,13 @@
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
     </row>
-    <row r="118" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-    </row>
   </sheetData>
   <autoFilter ref="A2:F2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E20" r:id="rId1" xr:uid="{454E9478-C493-4D1F-969F-203728E70B25}"/>
+    <hyperlink ref="E19" r:id="rId1" xr:uid="{454E9478-C493-4D1F-969F-203728E70B25}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" orientation="portrait" r:id="rId2"/>
